--- a/02-stakeholder-analysis/Preliminary_RACI_Matrix_P2P.xlsx
+++ b/02-stakeholder-analysis/Preliminary_RACI_Matrix_P2P.xlsx
@@ -10,9 +10,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Preliminary RACI Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preliminary RACI Matrix'!$A$8:$H$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Preliminary RACI Matrix'!$A$8:$I$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Preliminary RACI Matrix'!$A$1:$I$34</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -183,7 +184,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -205,11 +206,44 @@
         <color rgb="00E5E7EB"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -279,6 +313,55 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,9 +726,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -656,120 +739,135 @@
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Procure-to-Pay (P2P) System Implementation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Preliminary RACI Matrix — Business Responsibility &amp; Governance</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Note: Preliminary matrix. Detailed approval authority will later depend on business rules and approval thresholds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>R — Responsible</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>A — Accountable</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>C — Consulted</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>I — Informed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Performs the activity</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Ultimately owns outcome</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>Provides 2-way input</t>
-        </is>
-      </c>
-      <c r="G6" s="11" t="inlineStr">
-        <is>
-          <t>Receives status info</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="10" customHeight="1"/>
-    <row r="8" ht="28" customHeight="1">
+    <row r="1" ht="50" customHeight="1">
+      <c r="A1" s="29" t="inlineStr">
+        <is>
+          <t>Nghiên cứu tình huống phân tích nghiệp vụ (BA) quy trình mua hàng đến thanh toán (P2P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="50" customHeight="1">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>Ma trận trách nhiệm (RACI) sơ bộ của quy trình — Trách nhiệm con người và chủ thể chịu trách nhiệm chính sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="50" customHeight="1">
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>Ma trận vai trò con người: hệ thống tự động kiểm tra ngân sách và đối chiếu. Con người chịu trách nhiệm chính sách, điều phối nghiệp vụ và xem xét kết quả.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1"/>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>R — Thực hiện (Responsible)</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>A — Chịu trách nhiệm cuối cùng (Accountable)</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>C — Được tham vấn (Consulted)</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="34" t="inlineStr">
+        <is>
+          <t>I — Được thông báo (Informed)</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="35" t="inlineStr">
+        <is>
+          <t>Thực hiện hoạt động</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n"/>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>Chịu trách nhiệm cuối cùng về kết quả</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="n"/>
+      <c r="E6" s="37" t="inlineStr">
+        <is>
+          <t>Trao đổi thông tin hai chiều</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="n"/>
+      <c r="G6" s="38" t="inlineStr">
+        <is>
+          <t>Nhận thông tin trạng thái</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="n"/>
+    </row>
+    <row r="7" ht="48" customHeight="1"/>
+    <row r="8" ht="44" customHeight="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Hoạt động</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>Requester</t>
+          <t>Người yêu cầu</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Store Manager</t>
+          <t>Quản lý cửa hàng</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Procurement Officer</t>
+          <t>Nhân viên mua hàng</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Procurement Manager</t>
+          <t>Trưởng bộ phận mua hàng</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Warehouse Staff</t>
+          <t>Nhân viên kho</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>AP Accountant</t>
+          <t>Kế toán công nợ phải trả (AP)</t>
         </is>
       </c>
       <c r="H8" s="13" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Create and Submit PR</t>
+          <t>Trưởng bộ phận tài chính</t>
+        </is>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Kiểm toán nội bộ</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>Tạo và gửi yêu cầu mua hàng (PR)</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -807,11 +905,16 @@
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
-        <is>
-          <t>Approve Business Need / PR</t>
+      <c r="I9" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="25" t="inlineStr">
+        <is>
+          <t>Phê duyệt nhu cầu nghiệp vụ / PR</t>
         </is>
       </c>
       <c r="B10" s="16" t="inlineStr">
@@ -849,11 +952,16 @@
           <t>C*</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Validate Budget</t>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>Kiểm tra ngân sách</t>
         </is>
       </c>
       <c r="B11" s="16" t="inlineStr">
@@ -891,11 +999,16 @@
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
-        <is>
-          <t>Select Approved Supplier</t>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Chọn nhà cung cấp đã phê duyệt</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
@@ -933,11 +1046,16 @@
           <t>—</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Create Purchase Order</t>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t>Tạo đơn đặt hàng (PO)</t>
         </is>
       </c>
       <c r="B13" s="17" t="inlineStr">
@@ -975,11 +1093,16 @@
           <t>I</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
-        <is>
-          <t>Approve Purchase Order</t>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="25" t="inlineStr">
+        <is>
+          <t>Phê duyệt mua hàng cho PO</t>
         </is>
       </c>
       <c r="B14" s="16" t="inlineStr">
@@ -999,7 +1122,7 @@
       </c>
       <c r="E14" s="15" t="inlineStr">
         <is>
-          <t>R/A*</t>
+          <t>R/A</t>
         </is>
       </c>
       <c r="F14" s="19" t="inlineStr">
@@ -1014,64 +1137,74 @@
       </c>
       <c r="H14" s="15" t="inlineStr">
         <is>
-          <t>R/A*</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Record Goods Receipt</t>
-        </is>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="25" t="inlineStr">
+        <is>
+          <t>Phê duyệt tài chính bổ sung cho PO (có điều kiện)</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>Record / Validate Supplier Invoice</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>Ghi nhận phiếu nhận hàng (GR)</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1081,258 +1214,387 @@
           <t>I</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="E16" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G16" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I16" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Ghi nhận / Kiểm tra hóa đơn nhà cung cấp</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G16" s="15" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Perform Three-Way Matching</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="H17" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>Thực hiện đối chiếu ba bên</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
-        <is>
-          <t>Resolve Matching Exception</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="I18" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="25" t="inlineStr">
+        <is>
+          <t>Xử lý ngoại lệ đối chiếu</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>R/C</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>R/C</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Approve Payment Request</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>Phê duyệt đề nghị thanh toán</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E20" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>R/A</t>
         </is>
       </c>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
-        <is>
-          <t>Review Audit Evidence</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Rà soát bằng chứng kiểm toán</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H21" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="21" t="inlineStr">
-        <is>
-          <t>★ Business Rules &amp; Approval Threshold Note (*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="A23" s="22" t="inlineStr">
-        <is>
-          <t>• * Approval responsibility may change depending on approval thresholds and business rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="23" t="inlineStr">
-        <is>
-          <t>• Lower-value PO  →  Procurement Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="23" t="inlineStr">
-        <is>
-          <t>• Higher-value PO  →  Finance Manager</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>• High-value / Exceptional PO  →  CFO</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="23" t="inlineStr">
-        <is>
-          <t>• The exact thresholds are intentionally not finalized in the stakeholder analysis. They will be defined later in the Business Rules and To-Be process.</t>
+      <c r="I21" s="15" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Ghi chú tuyến phê duyệt PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>• Mọi PO đều phải được Trưởng bộ phận mua hàng phê duyệt mua hàng.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="40" t="inlineStr">
+        <is>
+          <t>• Phê duyệt của Trưởng bộ phận tài chính là bổ sung khi tiêu chí áp dụng yêu cầu.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="40" t="inlineStr">
+        <is>
+          <t>• Phải hoàn tất mọi phê duyệt bắt buộc trước khi phát hành PO; PO bị trả lại được chỉnh sửa và gửi lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>• CFO là nhà bảo trợ cấp điều hành và người rà soát tài liệu yêu cầu nghiệp vụ (BRD), không phê duyệt PO vận hành.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="40" t="inlineStr">
+        <is>
+          <t>• Ngưỡng và tiêu chí phê duyệt tài chính OD-01/OD-02 vẫn chưa chốt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="27" t="inlineStr">
+        <is>
+          <t>Ghi chú trách nhiệm và phạm vi — Đường cơ sở giả lập; chưa có ký duyệt của các bên liên quan</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="28" t="inlineStr">
+        <is>
+          <t>Kiểm tra ngân sách: Hệ thống quản lý mua hàng thực hiện UC-01/FR-02 bằng Nguồn dữ liệu ngân sách. Vai trò A của Tài chính chịu trách nhiệm chính sách/kiểm soát ngân sách, không tính toán thủ công.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="28" t="inlineStr">
+        <is>
+          <t>Đối chiếu: hệ thống thực hiện so sánh. AP với vai trò R điều phối khởi chạy và xem xét kết quả; Tài chính với vai trò A chịu trách nhiệm kết quả kiểm soát tài chính.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="28" t="inlineStr">
+        <is>
+          <t>R/C khi xử lý ngoại lệ: Mua hàng/Kho là R đối với thông tin điều tra/chỉnh sửa bắt buộc thuộc nghiệp vụ của mình và là C khi chỉ cần làm rõ. Không cấp quyền sửa trực tiếp chứng từ đã phê duyệt/phát hành.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="28" t="inlineStr">
+        <is>
+          <t>R/A kết hợp cả hai vai trò. C* là tham vấn Tài chính để làm rõ kiểm soát tài chính của PR; Quản lý cửa hàng vẫn quyết định nghiệp vụ. Không thêm bước Tài chính phê duyệt PR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="28" t="inlineStr">
+        <is>
+          <t>Rà soát bằng chứng kiểm toán: Kiểm toán nội bộ R/A phản ánh UC-11. Mua hàng/Tài chính cũng có thể xem lịch sử trong quyền được cấp; phạm vi truy cập vẫn cần xác định theo OD-07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
+          <t>RACI quy trình này khác RACI rà soát/ký duyệt BRD. R/A không cấp quyền hệ thống. Chi tiết chỉnh sửa/chuyển cấp và chủ thể chịu trách nhiệm trường hợp hỗn hợp vẫn chưa chốt.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A8:H20"/>
-  <mergeCells count="17">
-    <mergeCell ref="A3:H3"/>
+  <autoFilter ref="A8:I21"/>
+  <mergeCells count="24">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A29:I29"/>
     <mergeCell ref="E6:F6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A28:I28"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="A24:I24"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
 </file>